--- a/DemoTestData.xlsx
+++ b/DemoTestData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iulaganathan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iulaganathan\apache-jmeter-5.6.2\bin\Iyyappan_Mini_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAAEBDE8-D7C5-4AEC-A901-8F764F5FB959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B72BBF9-4CE4-45EB-8CBB-FB7137C5EC35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D9ED8855-CA30-4573-B9A0-765822E9D7F5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
   <si>
     <t>VpinValue</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>English</t>
+  </si>
+  <si>
+    <t>Inida</t>
   </si>
 </sst>
 </file>
@@ -431,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B914249-1B09-41D0-9F46-C6FDBB5BAC13}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.54296875" customWidth="1"/>
@@ -465,6 +468,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
